--- a/data/trans_dic/IP19C03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por empastes</t>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 31,95</t>
+          <t>5,33; 30,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 37,18</t>
+          <t>6,83; 35,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,76; 43,56</t>
+          <t>14,74; 43,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,8; 50,74</t>
+          <t>22,97; 50,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,2; 38,83</t>
+          <t>9,16; 37,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,51; 41,02</t>
+          <t>14,1; 39,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 27,71</t>
+          <t>6,11; 27,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,25; 45,9</t>
+          <t>19,93; 46,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 31,15</t>
+          <t>11,25; 29,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,59; 34,21</t>
+          <t>14,26; 32,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,9; 31,44</t>
+          <t>13,2; 30,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,43; 44,52</t>
+          <t>24,55; 44,28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,46; 31,87</t>
+          <t>14,07; 31,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 15,43</t>
+          <t>2,96; 16,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,68; 30,8</t>
+          <t>12,81; 32,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,0; 40,73</t>
+          <t>17,34; 42,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 31,36</t>
+          <t>14,51; 30,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,61; 28,39</t>
+          <t>11,26; 28,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,52; 39,41</t>
+          <t>19,89; 38,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,36; 36,04</t>
+          <t>15,41; 36,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,67; 28,74</t>
+          <t>16,58; 28,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 19,63</t>
+          <t>9,28; 20,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 31,9</t>
+          <t>18,4; 31,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 33,35</t>
+          <t>18,85; 33,74</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,89; 40,59</t>
+          <t>14,79; 40,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 22,34</t>
+          <t>4,12; 21,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 21,39</t>
+          <t>2,13; 19,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 19,32</t>
+          <t>3,27; 18,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,71; 26,52</t>
+          <t>7,1; 26,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 22,12</t>
+          <t>4,93; 22,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 21,03</t>
+          <t>2,53; 21,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 27,63</t>
+          <t>6,99; 27,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,82; 29,43</t>
+          <t>13,47; 29,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 18,4</t>
+          <t>6,28; 17,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 16,44</t>
+          <t>3,48; 16,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 19,69</t>
+          <t>6,06; 19,2</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 31,18</t>
+          <t>12,14; 32,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,03; 39,6</t>
+          <t>17,04; 40,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,51; 31,28</t>
+          <t>12,78; 32,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 32,89</t>
+          <t>10,07; 32,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 23,87</t>
+          <t>6,72; 24,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 31,41</t>
+          <t>10,4; 30,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 22,23</t>
+          <t>6,17; 22,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 27,32</t>
+          <t>4,16; 27,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 25,29</t>
+          <t>11,87; 25,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,57; 31,89</t>
+          <t>16,6; 31,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 23,31</t>
+          <t>11,16; 23,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 24,35</t>
+          <t>9,2; 25,45</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 32,73</t>
+          <t>7,57; 32,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 27,51</t>
+          <t>5,25; 28,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,28; 51,37</t>
+          <t>12,75; 50,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 28,15</t>
+          <t>8,71; 28,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,41; 37,63</t>
+          <t>9,31; 37,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 19,43</t>
+          <t>2,33; 18,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 43,11</t>
+          <t>8,26; 42,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 22,59</t>
+          <t>4,91; 23,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 30,3</t>
+          <t>11,22; 30,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 19,06</t>
+          <t>5,03; 17,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,71; 38,49</t>
+          <t>14,3; 38,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 21,38</t>
+          <t>8,82; 21,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 39,01</t>
+          <t>11,26; 38,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,34; 31,5</t>
+          <t>8,39; 30,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 14,42</t>
+          <t>1,63; 14,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 22,51</t>
+          <t>3,98; 22,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 22,84</t>
+          <t>4,32; 22,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,37; 26,15</t>
+          <t>4,8; 27,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,65; 18,92</t>
+          <t>3,67; 19,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 25,52</t>
+          <t>4,73; 27,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 25,72</t>
+          <t>9,81; 26,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 24,09</t>
+          <t>9,39; 24,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 13,81</t>
+          <t>3,56; 12,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 20,3</t>
+          <t>6,1; 19,29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,32; 21,69</t>
+          <t>7,61; 22,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 26,1</t>
+          <t>10,21; 26,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 10,6</t>
+          <t>1,99; 11,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,48; 27,05</t>
+          <t>11,5; 27,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,99; 21,93</t>
+          <t>7,96; 21,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,04; 23,86</t>
+          <t>9,71; 25,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,34; 21,77</t>
+          <t>6,59; 22,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,51; 27,92</t>
+          <t>13,44; 27,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 20,16</t>
+          <t>9,84; 19,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,73; 22,14</t>
+          <t>11,62; 22,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 13,85</t>
+          <t>5,02; 14,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,46; 25,36</t>
+          <t>14,44; 25,06</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,35; 32,69</t>
+          <t>17,38; 33,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,7; 46,12</t>
+          <t>28,7; 46,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,51; 34,93</t>
+          <t>19,59; 34,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,48</t>
+          <t>3,01; 12,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,93; 27,26</t>
+          <t>13,02; 27,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,57; 42,08</t>
+          <t>23,88; 42,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,46; 35,65</t>
+          <t>19,22; 35,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,78; 11,29</t>
+          <t>2,84; 11,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,71; 28,2</t>
+          <t>17,53; 27,61</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,7; 41,04</t>
+          <t>28,69; 41,58</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,12; 32,56</t>
+          <t>21,07; 32,73</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,45</t>
+          <t>3,59; 9,6</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,27; 24,45</t>
+          <t>17,59; 24,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,58; 24,13</t>
+          <t>17,28; 24,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,77; 20,23</t>
+          <t>13,99; 20,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,61; 21,23</t>
+          <t>14,41; 21,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,63</t>
+          <t>14,43; 21,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,99; 22,91</t>
+          <t>15,88; 22,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,83</t>
+          <t>14,87; 21,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,8</t>
+          <t>13,49; 19,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,81; 21,81</t>
+          <t>16,96; 21,34</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,74; 22,31</t>
+          <t>17,62; 22,62</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,38; 19,96</t>
+          <t>15,58; 20,21</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,27</t>
+          <t>14,4; 19,4</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2946</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7860</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12594</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7841</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4272</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12541</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8977</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12058</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12132</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>25135</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1030; 5941</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1529; 7914</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4210; 12477</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7999; 17660</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2428; 9894</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4263; 11876</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1828; 8223</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7947; 18408</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5155; 13622</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7500; 17253</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7718; 17934</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>18337; 33067</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12408</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11289</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18606</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14288</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10762</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16365</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>17730</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>26696</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27654</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>36336</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8053; 18181</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1571; 8734</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6852; 17489</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>11940; 28983</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9428; 20113</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6492; 16602</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11436; 22139</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11378; 26809</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>20262; 35156</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10269; 22149</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>20427; 35080</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>26889; 48138</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8857</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3519</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5591</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4587</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2987</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5834</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14448</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5428</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8584</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>5071; 13982</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1378; 7236</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>694; 6435</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1042; 5760</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2508; 9321</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1945; 8680</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>813; 6816</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2798; 10995</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9380; 20797</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4580; 12864</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2248; 10749</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4356; 13797</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8942</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11445</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9530</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8294</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7794</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6535</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7871</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14507</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19239</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>16066</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>16165</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5094; 13489</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7013; 16694</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5948; 15266</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4312; 14124</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2797; 9996</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4288; 12661</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3145; 11702</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2442; 15865</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9925; 20900</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>13674; 26175</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>10891; 22569</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9341; 25837</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4827</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3524</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4236</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4210</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4909</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3896</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4019</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>9737</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5635</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8132</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8229</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1983; 8436</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1368; 7374</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1918; 7553</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2204; 7227</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2092; 8433</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>644; 5233</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1409; 7278</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1699; 8032</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>5457; 14610</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2699; 9610</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4593; 12465</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5286; 13123</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>5644</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6347</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2087</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3793</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3477</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>8753</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10764</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6315</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2854; 9809</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2971; 10737</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>646; 5711</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1074; 5957</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1225; 6399</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1593; 8968</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1488; 7773</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1274; 7513</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>5268; 14075</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>6442; 16815</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2857; 10224</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>3286; 10396</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>9099</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10938</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3516</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>14421</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10517</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>7977</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>21230</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>18623</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>21455</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>11493</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>35651</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4965; 14438</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6529; 17118</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1343; 7683</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8940; 21152</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5418; 14907</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6524; 16794</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4084; 13824</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>14609; 30106</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>13122; 25779</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>15235; 29634</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>6502; 18275</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>26916; 46730</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>20065</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>28692</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>20672</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5193</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>14454</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>23091</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>21265</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>6085</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>34519</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>51783</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>41938</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>11278</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>14136; 26903</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>22342; 35829</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>15526; 27299</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2503; 10704</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>9685; 20362</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>16738; 29653</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>15117; 27765</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2889; 11655</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>27299; 43000</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>42435; 61508</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>33271; 51681</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>6643; 17769</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>72789</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>72944</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>61631</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>68906</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>78788</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>136260</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>144064</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>128721</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>147694</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>61716; 87218</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>61062; 85384</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>50723; 73943</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>56430; 84026</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>52195; 76163</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>58221; 83474</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>54839; 79158</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>65330; 96364</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>120886; 152067</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>126829; 162877</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>113958; 147795</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>126168; 169935</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 30,75</t>
+          <t>5,79; 32,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 35,37</t>
+          <t>6,68; 34,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 43,68</t>
+          <t>15,48; 43,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,97; 50,72</t>
+          <t>22,33; 50,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 37,31</t>
+          <t>11,44; 38,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,1; 39,29</t>
+          <t>15,4; 41,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 27,49</t>
+          <t>6,32; 28,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,93; 46,18</t>
+          <t>18,3; 46,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,25; 29,72</t>
+          <t>11,67; 31,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 32,8</t>
+          <t>13,6; 33,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,2; 30,67</t>
+          <t>12,45; 29,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,55; 44,28</t>
+          <t>23,81; 44,15</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,07; 31,77</t>
+          <t>13,5; 30,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 16,47</t>
+          <t>3,71; 15,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 32,69</t>
+          <t>12,83; 30,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,34; 42,1</t>
+          <t>17,41; 40,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,51; 30,95</t>
+          <t>14,47; 30,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,26; 28,81</t>
+          <t>11,01; 27,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,89; 38,51</t>
+          <t>19,81; 39,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 36,31</t>
+          <t>14,42; 35,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,58; 28,77</t>
+          <t>16,1; 28,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 20,01</t>
+          <t>8,58; 19,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 31,61</t>
+          <t>18,9; 32,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,85; 33,74</t>
+          <t>19,08; 34,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,79; 40,77</t>
+          <t>15,3; 40,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 21,62</t>
+          <t>4,12; 23,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 19,79</t>
+          <t>2,06; 19,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 18,1</t>
+          <t>3,36; 20,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 26,38</t>
+          <t>8,07; 26,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 22,01</t>
+          <t>4,94; 21,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 21,22</t>
+          <t>2,27; 21,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 27,45</t>
+          <t>7,2; 26,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,47; 29,87</t>
+          <t>13,52; 29,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,28; 17,64</t>
+          <t>5,95; 18,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 16,63</t>
+          <t>3,5; 16,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 19,2</t>
+          <t>6,54; 19,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,14; 32,15</t>
+          <t>13,76; 32,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 40,56</t>
+          <t>17,37; 41,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,78; 32,8</t>
+          <t>11,95; 30,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 32,97</t>
+          <t>10,12; 33,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 24,01</t>
+          <t>6,39; 24,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 30,71</t>
+          <t>10,55; 30,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 22,94</t>
+          <t>6,3; 22,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 27,05</t>
+          <t>5,11; 28,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 25,0</t>
+          <t>12,18; 25,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,6; 31,77</t>
+          <t>16,25; 32,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,16; 23,14</t>
+          <t>10,95; 23,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 25,45</t>
+          <t>9,22; 24,31</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,57; 32,21</t>
+          <t>7,42; 32,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 28,29</t>
+          <t>5,23; 25,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,75; 50,21</t>
+          <t>12,79; 52,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 28,57</t>
+          <t>7,74; 28,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 37,53</t>
+          <t>9,35; 37,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 18,94</t>
+          <t>2,34; 20,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 42,64</t>
+          <t>8,18; 42,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 23,19</t>
+          <t>5,09; 23,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 30,02</t>
+          <t>11,49; 29,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 17,9</t>
+          <t>4,38; 18,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,3; 38,82</t>
+          <t>14,25; 39,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,82; 21,9</t>
+          <t>8,13; 21,13</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,26; 38,71</t>
+          <t>10,63; 38,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,39; 30,31</t>
+          <t>8,8; 29,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 14,37</t>
+          <t>1,6; 13,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,98; 22,1</t>
+          <t>3,97; 21,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,32; 22,57</t>
+          <t>4,29; 23,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 27,05</t>
+          <t>4,65; 26,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 19,16</t>
+          <t>3,69; 21,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,73; 27,88</t>
+          <t>4,85; 27,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 26,21</t>
+          <t>9,69; 25,87</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 24,52</t>
+          <t>9,14; 24,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 12,73</t>
+          <t>3,59; 13,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,1; 19,29</t>
+          <t>5,74; 19,41</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 22,12</t>
+          <t>8,23; 22,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,21; 26,76</t>
+          <t>10,65; 26,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 11,39</t>
+          <t>1,96; 11,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,5; 27,2</t>
+          <t>11,35; 26,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 21,91</t>
+          <t>8,02; 21,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,71; 25,01</t>
+          <t>9,46; 24,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 22,32</t>
+          <t>6,31; 21,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,44; 27,7</t>
+          <t>12,51; 27,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,84; 19,34</t>
+          <t>9,71; 19,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,62; 22,6</t>
+          <t>11,49; 22,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 14,12</t>
+          <t>5,19; 13,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,44; 25,06</t>
+          <t>14,77; 24,88</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,38; 33,08</t>
+          <t>17,4; 32,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,7; 46,03</t>
+          <t>27,94; 44,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,59; 34,45</t>
+          <t>18,32; 34,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,01; 12,85</t>
+          <t>2,94; 11,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,02; 27,36</t>
+          <t>12,99; 27,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,88; 42,31</t>
+          <t>23,73; 42,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,22; 35,3</t>
+          <t>18,97; 35,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 11,45</t>
+          <t>2,9; 11,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,53; 27,61</t>
+          <t>17,57; 28,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,69; 41,58</t>
+          <t>28,85; 41,14</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,07; 32,73</t>
+          <t>21,35; 32,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,6</t>
+          <t>3,6; 9,45</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,59; 24,85</t>
+          <t>17,8; 24,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,28; 24,16</t>
+          <t>17,13; 24,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,99; 20,39</t>
+          <t>14,16; 20,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,41; 21,46</t>
+          <t>14,03; 21,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,43; 21,06</t>
+          <t>14,62; 20,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,88; 22,77</t>
+          <t>16,33; 22,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,87; 21,47</t>
+          <t>15,14; 21,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,89</t>
+          <t>13,07; 19,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,96; 21,34</t>
+          <t>16,79; 21,44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,62; 22,62</t>
+          <t>17,47; 22,37</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,58; 20,21</t>
+          <t>15,39; 19,87</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,4</t>
+          <t>14,79; 19,38</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1030; 5941</t>
+          <t>1120; 6184</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1529; 7914</t>
+          <t>1494; 7821</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4210; 12477</t>
+          <t>4421; 12563</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7999; 17660</t>
+          <t>7776; 17473</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2428; 9894</t>
+          <t>3033; 10199</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4263; 11876</t>
+          <t>4655; 12565</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1828; 8223</t>
+          <t>1891; 8569</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7947; 18408</t>
+          <t>7294; 18385</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5155; 13622</t>
+          <t>5350; 14261</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7500; 17253</t>
+          <t>7154; 17605</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7718; 17934</t>
+          <t>7280; 17516</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18337; 33067</t>
+          <t>17781; 32969</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8053; 18181</t>
+          <t>7723; 17604</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1571; 8734</t>
+          <t>1968; 8462</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6852; 17489</t>
+          <t>6868; 16532</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11940; 28983</t>
+          <t>11988; 27872</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9428; 20113</t>
+          <t>9399; 20070</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6492; 16602</t>
+          <t>6346; 16002</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11436; 22139</t>
+          <t>11387; 22493</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11378; 26809</t>
+          <t>10648; 25902</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20262; 35156</t>
+          <t>19678; 34319</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10269; 22149</t>
+          <t>9498; 21535</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20427; 35080</t>
+          <t>20980; 36323</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26889; 48138</t>
+          <t>27224; 49112</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5071; 13982</t>
+          <t>5248; 13975</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1378; 7236</t>
+          <t>1380; 7747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>694; 6435</t>
+          <t>671; 6485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1042; 5760</t>
+          <t>1069; 6372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2508; 9321</t>
+          <t>2852; 9436</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1945; 8680</t>
+          <t>1949; 8549</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>813; 6816</t>
+          <t>729; 6799</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2798; 10995</t>
+          <t>2883; 10699</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9380; 20797</t>
+          <t>9410; 20566</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4580; 12864</t>
+          <t>4339; 13234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2248; 10749</t>
+          <t>2265; 10425</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4356; 13797</t>
+          <t>4703; 14313</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5094; 13489</t>
+          <t>5772; 13836</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7013; 16694</t>
+          <t>7149; 16974</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5948; 15266</t>
+          <t>5564; 14385</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4312; 14124</t>
+          <t>4334; 14230</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2797; 9996</t>
+          <t>2661; 10000</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4288; 12661</t>
+          <t>4350; 12547</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3145; 11702</t>
+          <t>3213; 11285</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2442; 15865</t>
+          <t>2998; 16708</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9925; 20900</t>
+          <t>10184; 21197</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13674; 26175</t>
+          <t>13387; 26588</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10891; 22569</t>
+          <t>10677; 22495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9341; 25837</t>
+          <t>9357; 24676</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1983; 8436</t>
+          <t>1943; 8468</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1368; 7374</t>
+          <t>1362; 6530</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1918; 7553</t>
+          <t>1923; 7913</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2204; 7227</t>
+          <t>1958; 7179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2092; 8433</t>
+          <t>2100; 8535</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>644; 5233</t>
+          <t>646; 5785</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1409; 7278</t>
+          <t>1396; 7256</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1699; 8032</t>
+          <t>1762; 8047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5457; 14610</t>
+          <t>5591; 14582</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2699; 9610</t>
+          <t>2350; 9982</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4593; 12465</t>
+          <t>4576; 12606</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5286; 13123</t>
+          <t>4871; 12663</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2854; 9809</t>
+          <t>2693; 9726</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2971; 10737</t>
+          <t>3118; 10366</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646; 5711</t>
+          <t>634; 5414</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1074; 5957</t>
+          <t>1070; 5922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1225; 6399</t>
+          <t>1217; 6803</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1593; 8968</t>
+          <t>1540; 8939</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1488; 7773</t>
+          <t>1498; 8871</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1274; 7513</t>
+          <t>1307; 7317</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5268; 14075</t>
+          <t>5203; 13891</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6442; 16815</t>
+          <t>6267; 16684</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2857; 10224</t>
+          <t>2881; 10787</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3286; 10396</t>
+          <t>3096; 10464</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4965; 14438</t>
+          <t>5371; 14594</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6529; 17118</t>
+          <t>6815; 16875</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1343; 7683</t>
+          <t>1323; 7860</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8940; 21152</t>
+          <t>8827; 20587</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5418; 14907</t>
+          <t>5459; 14446</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6524; 16794</t>
+          <t>6355; 16180</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4084; 13824</t>
+          <t>3910; 13341</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14609; 30106</t>
+          <t>13593; 30053</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13122; 25779</t>
+          <t>12940; 25986</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15235; 29634</t>
+          <t>15074; 28905</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6502; 18275</t>
+          <t>6718; 18099</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26916; 46730</t>
+          <t>27531; 46379</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14136; 26903</t>
+          <t>14146; 26400</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>22342; 35829</t>
+          <t>21754; 34982</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15526; 27299</t>
+          <t>14522; 27293</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2503; 10704</t>
+          <t>2445; 9862</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9685; 20362</t>
+          <t>9667; 20258</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16738; 29653</t>
+          <t>16629; 29517</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15117; 27765</t>
+          <t>14923; 28229</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2889; 11655</t>
+          <t>2948; 11834</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27299; 43000</t>
+          <t>27369; 43622</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>42435; 61508</t>
+          <t>42673; 60862</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33271; 51681</t>
+          <t>33709; 51575</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6643; 17769</t>
+          <t>6671; 17488</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>61716; 87218</t>
+          <t>62455; 85858</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>61062; 85384</t>
+          <t>60546; 84849</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50723; 73943</t>
+          <t>51337; 73260</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56430; 84026</t>
+          <t>54937; 82922</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>52195; 76163</t>
+          <t>52878; 75264</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58221; 83474</t>
+          <t>59864; 83812</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>54839; 79158</t>
+          <t>55840; 81047</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>65330; 96364</t>
+          <t>63316; 94934</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>120886; 152067</t>
+          <t>119633; 152819</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>126829; 162877</t>
+          <t>125795; 161024</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>113958; 147795</t>
+          <t>112577; 145356</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>126168; 169935</t>
+          <t>129528; 169743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C03-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22,74%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25,94%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29,17%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15,25%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18,85%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>27,52%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36,17%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 32,01</t>
+          <t>11,2; 38,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 34,96</t>
+          <t>14,51; 41,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,48; 43,98</t>
+          <t>5,34; 27,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,33; 50,18</t>
+          <t>17,28; 42,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,44; 38,46</t>
+          <t>5,62; 31,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,4; 41,56</t>
+          <t>7,07; 37,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 28,65</t>
+          <t>15,76; 43,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,3; 46,12</t>
+          <t>25,61; 52,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,67; 31,11</t>
+          <t>11,18; 31,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 33,47</t>
+          <t>14,59; 34,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 29,95</t>
+          <t>12,9; 31,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,81; 44,15</t>
+          <t>25,46; 44,9</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18,67%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28,47%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24,65%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>21,68%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,03%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>21,1%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>28,47%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,5; 30,76</t>
+          <t>14,63; 31,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 15,95</t>
+          <t>11,61; 28,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,83; 30,9</t>
+          <t>19,52; 39,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 40,49</t>
+          <t>15,67; 36,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 30,89</t>
+          <t>14,46; 31,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,01; 27,77</t>
+          <t>3,59; 15,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,81; 39,13</t>
+          <t>12,68; 30,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,42; 35,08</t>
+          <t>15,85; 33,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,1; 28,08</t>
+          <t>16,67; 28,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 19,46</t>
+          <t>9,24; 19,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,9; 32,73</t>
+          <t>18,83; 31,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,08; 34,42</t>
+          <t>17,53; 31,49</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>25,83%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,51%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,3; 40,75</t>
+          <t>8,71; 26,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 23,15</t>
+          <t>4,95; 22,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 19,94</t>
+          <t>2,52; 21,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 20,02</t>
+          <t>6,55; 27,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 26,71</t>
+          <t>14,89; 40,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 21,67</t>
+          <t>4,19; 22,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 21,16</t>
+          <t>2,17; 21,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 26,71</t>
+          <t>3,66; 20,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 29,54</t>
+          <t>13,82; 29,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 18,15</t>
+          <t>6,37; 18,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 16,13</t>
+          <t>3,52; 16,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 19,91</t>
+          <t>6,77; 19,46</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13,36%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>21,31%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>27,8%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20,48%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,76; 32,97</t>
+          <t>6,52; 23,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 41,24</t>
+          <t>10,47; 31,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,95; 30,91</t>
+          <t>6,87; 22,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 33,21</t>
+          <t>5,4; 29,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 24,02</t>
+          <t>12,59; 31,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,55; 30,44</t>
+          <t>16,03; 39,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 22,13</t>
+          <t>12,51; 31,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 28,48</t>
+          <t>9,7; 32,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 25,35</t>
+          <t>11,36; 25,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,25; 32,27</t>
+          <t>16,57; 31,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,95; 23,06</t>
+          <t>11,04; 23,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 24,31</t>
+          <t>8,97; 25,03</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,85%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>18,43%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13,52%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>28,15%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16,65%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 32,33</t>
+          <t>9,41; 37,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 25,05</t>
+          <t>2,35; 19,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,79; 52,6</t>
+          <t>8,44; 43,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 28,38</t>
+          <t>5,03; 22,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 37,99</t>
+          <t>7,69; 32,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 20,94</t>
+          <t>5,26; 27,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 42,51</t>
+          <t>12,28; 51,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 23,24</t>
+          <t>7,66; 28,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,49; 29,97</t>
+          <t>11,45; 30,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 18,59</t>
+          <t>5,13; 19,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,25; 39,26</t>
+          <t>13,71; 38,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 21,13</t>
+          <t>8,47; 21,78</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22,27%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5,25%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,63; 38,38</t>
+          <t>4,35; 22,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,8; 29,26</t>
+          <t>6,37; 26,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,62</t>
+          <t>3,65; 18,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,97; 21,96</t>
+          <t>4,73; 24,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,29; 23,99</t>
+          <t>10,82; 39,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,65; 26,96</t>
+          <t>8,34; 31,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 21,86</t>
+          <t>1,63; 14,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,85; 27,15</t>
+          <t>4,1; 22,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,69; 25,87</t>
+          <t>9,25; 25,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,14; 24,33</t>
+          <t>9,56; 24,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,59; 13,43</t>
+          <t>3,52; 13,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,74; 19,41</t>
+          <t>6,22; 20,06</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>13,94%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>17,1%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,21%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18,55%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 22,36</t>
+          <t>7,99; 21,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,65; 26,38</t>
+          <t>9,04; 23,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 11,65</t>
+          <t>6,34; 21,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,35; 26,48</t>
+          <t>12,91; 27,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,02; 21,23</t>
+          <t>8,32; 21,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 24,09</t>
+          <t>9,21; 26,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 21,54</t>
+          <t>2,01; 10,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,51; 27,65</t>
+          <t>13,04; 28,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,71; 19,49</t>
+          <t>9,73; 20,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,49; 22,04</t>
+          <t>11,73; 22,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 13,99</t>
+          <t>4,97; 13,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,77; 24,88</t>
+          <t>14,99; 26,13</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19,42%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32,95%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27,04%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>24,67%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>36,86%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>26,08%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>19,42%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>32,95%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,4; 32,46</t>
+          <t>12,93; 27,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,94; 44,94</t>
+          <t>24,57; 42,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,32; 34,44</t>
+          <t>19,46; 35,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 11,84</t>
+          <t>2,49; 10,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,99; 27,22</t>
+          <t>17,35; 32,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,73; 42,11</t>
+          <t>28,7; 46,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,97; 35,89</t>
+          <t>18,51; 34,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,63</t>
+          <t>2,44; 11,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,57; 28,01</t>
+          <t>17,71; 28,2</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,85; 41,14</t>
+          <t>28,7; 41,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,35; 32,66</t>
+          <t>21,12; 32,56</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,45</t>
+          <t>3,23; 8,65</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>20,74%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>20,64%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,8; 24,47</t>
+          <t>14,55; 20,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,13; 24,01</t>
+          <t>15,99; 22,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14,16; 20,2</t>
+          <t>15,31; 21,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,03; 21,17</t>
+          <t>12,59; 19,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,62; 20,81</t>
+          <t>17,27; 24,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,33; 22,86</t>
+          <t>17,58; 24,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,14; 21,98</t>
+          <t>13,77; 20,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,07; 19,6</t>
+          <t>14,04; 20,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,79; 21,44</t>
+          <t>16,81; 21,81</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,47; 22,37</t>
+          <t>17,74; 22,31</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15,39; 19,87</t>
+          <t>15,38; 19,96</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,79; 19,38</t>
+          <t>14,34; 18,67</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7841</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4272</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9718</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2946</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4217</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>7860</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12594</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6030</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7841</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4272</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25135</t>
+          <t>21433</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1120; 6184</t>
+          <t>2970; 10296</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1494; 7821</t>
+          <t>4386; 12401</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4421; 12563</t>
+          <t>1597; 8287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7776; 17473</t>
+          <t>5756; 14291</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3033; 10199</t>
+          <t>1086; 6173</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4655; 12565</t>
+          <t>1582; 8320</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1891; 8569</t>
+          <t>4502; 12444</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7294; 18385</t>
+          <t>7552; 15604</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5350; 14261</t>
+          <t>5127; 14278</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7154; 17605</t>
+          <t>7676; 17995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7280; 17516</t>
+          <t>7541; 18386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17781; 32969</t>
+          <t>15992; 28198</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14288</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10762</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16365</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12408</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4261</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11289</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18606</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14288</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10762</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16365</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36336</t>
+          <t>33502</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7723; 17604</t>
+          <t>9504; 20375</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1968; 8462</t>
+          <t>6691; 16362</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6868; 16532</t>
+          <t>11221; 22656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11988; 27872</t>
+          <t>10847; 25512</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9399; 20070</t>
+          <t>8273; 18236</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6346; 16002</t>
+          <t>1906; 8182</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11387; 22493</t>
+          <t>6783; 16482</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10648; 25902</t>
+          <t>10781; 22893</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19678; 34319</t>
+          <t>20376; 35114</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9498; 21535</t>
+          <t>10222; 21731</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20980; 36323</t>
+          <t>20904; 35404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27224; 49112</t>
+          <t>24057; 43215</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5591</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4587</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2987</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5055</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8857</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3519</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2441</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2750</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5591</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4587</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2987</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>7985</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5248; 13975</t>
+          <t>3075; 9369</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1380; 7747</t>
+          <t>1954; 8726</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>671; 6485</t>
+          <t>809; 6754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1069; 6372</t>
+          <t>2324; 9702</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2852; 9436</t>
+          <t>5107; 13920</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1949; 8549</t>
+          <t>1403; 7476</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>729; 6799</t>
+          <t>707; 6954</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2883; 10699</t>
+          <t>1156; 6466</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9410; 20566</t>
+          <t>9621; 20487</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4339; 13234</t>
+          <t>4644; 13415</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2265; 10425</t>
+          <t>2275; 10629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4703; 14313</t>
+          <t>4538; 13041</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7794</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6535</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7639</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>8942</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>11445</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9530</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8294</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5565</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7794</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6535</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16272</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5772; 13836</t>
+          <t>2715; 9941</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7149; 16974</t>
+          <t>4315; 12950</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5564; 14385</t>
+          <t>3502; 11339</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4334; 14230</t>
+          <t>2925; 15842</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2661; 10000</t>
+          <t>5284; 13084</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4350; 12547</t>
+          <t>6598; 16301</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3213; 11285</t>
+          <t>5824; 14560</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2998; 16708</t>
+          <t>4399; 14724</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10184; 21197</t>
+          <t>9499; 21143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13387; 26588</t>
+          <t>13649; 26273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10677; 22495</t>
+          <t>10767; 22735</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9357; 24676</t>
+          <t>8932; 24907</t>
         </is>
       </c>
     </row>
@@ -2910,37 +2910,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4909</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2111</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3896</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3952</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>4827</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3524</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4236</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4210</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4909</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3896</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>8391</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1943; 8468</t>
+          <t>2114; 8455</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1362; 6530</t>
+          <t>648; 5367</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1923; 7913</t>
+          <t>1441; 7359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1958; 7179</t>
+          <t>1686; 7530</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2100; 8535</t>
+          <t>2013; 8572</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>646; 5785</t>
+          <t>1372; 7170</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1396; 7256</t>
+          <t>1848; 7728</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1762; 8047</t>
+          <t>2029; 7485</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5591; 14582</t>
+          <t>5569; 14745</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2350; 9982</t>
+          <t>2752; 10236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4576; 12606</t>
+          <t>4402; 12361</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4871; 12663</t>
+          <t>5085; 13073</t>
         </is>
       </c>
     </row>
@@ -3113,37 +3113,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4417</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3793</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5644</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6347</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2087</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2838</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3109</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4417</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3793</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6062</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2693; 9726</t>
+          <t>1234; 6478</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3118; 10366</t>
+          <t>2113; 8672</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>634; 5414</t>
+          <t>1479; 7674</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1070; 5922</t>
+          <t>1152; 5919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1217; 6803</t>
+          <t>2743; 9885</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1540; 8939</t>
+          <t>2955; 11158</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1498; 8871</t>
+          <t>648; 5732</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1307; 7317</t>
+          <t>1140; 6341</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5203; 13891</t>
+          <t>4968; 13809</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6267; 16684</t>
+          <t>6557; 16519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2881; 10787</t>
+          <t>2827; 11090</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3096; 10464</t>
+          <t>3244; 10458</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>10517</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7977</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>20508</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>9099</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>10938</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>3516</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>14421</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>9524</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>10517</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>7977</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>35377</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5371; 14594</t>
+          <t>5435; 14919</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6815; 16875</t>
+          <t>6075; 16025</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1323; 7860</t>
+          <t>3928; 13485</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8827; 20587</t>
+          <t>13248; 28630</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5459; 14446</t>
+          <t>5429; 14157</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6355; 16180</t>
+          <t>5889; 16697</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3910; 13341</t>
+          <t>1357; 7148</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13593; 30053</t>
+          <t>9920; 21684</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12940; 25986</t>
+          <t>12971; 26870</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15074; 28905</t>
+          <t>15378; 29039</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6718; 18099</t>
+          <t>6430; 17924</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27531; 46379</t>
+          <t>26790; 46695</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>14454</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>23091</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>21265</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5898</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>20065</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>28692</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>20672</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5193</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>14454</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>23091</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>21265</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11159</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14146; 26400</t>
+          <t>9622; 20283</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21754; 34982</t>
+          <t>17223; 29489</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14522; 27293</t>
+          <t>15307; 28040</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2445; 9862</t>
+          <t>2702; 11510</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9667; 20258</t>
+          <t>14111; 26585</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16629; 29517</t>
+          <t>22343; 35901</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14923; 28229</t>
+          <t>14670; 27680</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2948; 11834</t>
+          <t>2233; 10806</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27369; 43622</t>
+          <t>27574; 43909</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>42673; 60862</t>
+          <t>42462; 60714</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33709; 51575</t>
+          <t>33349; 51408</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6671; 17488</t>
+          <t>6462; 17295</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>97</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>72870</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>72789</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>72944</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>61631</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>68906</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>63471</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>71120</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>67090</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>78788</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>147694</t>
+          <t>140182</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>62455; 85858</t>
+          <t>52631; 74619</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>60546; 84849</t>
+          <t>58627; 83973</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51337; 73260</t>
+          <t>56471; 80516</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54937; 82922</t>
+          <t>58072; 88226</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>52878; 75264</t>
+          <t>60600; 85800</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>59864; 83812</t>
+          <t>62117; 85259</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55840; 81047</t>
+          <t>49923; 73348</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>63316; 94934</t>
+          <t>55645; 79711</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>119633; 152819</t>
+          <t>119807; 155465</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>125795; 161024</t>
+          <t>127695; 160607</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>112577; 145356</t>
+          <t>112503; 146019</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>129528; 169743</t>
+          <t>122944; 160070</t>
         </is>
       </c>
     </row>
